--- a/DataTables/Datas/#UIPanel.xlsx
+++ b/DataTables/Datas/#UIPanel.xlsx
@@ -85,7 +85,7 @@
     <t>SettingPanel</t>
   </si>
   <si>
-    <t>Bottom_2</t>
+    <t>Bottom2</t>
   </si>
   <si>
     <t>设置界面</t>

--- a/DataTables/Datas/#UIPanel.xlsx
+++ b/DataTables/Datas/#UIPanel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>设置界面</t>
+  </si>
+  <si>
+    <t>BattlePanel</t>
+  </si>
+  <si>
+    <t>战斗界面</t>
   </si>
 </sst>
 </file>
@@ -1051,8 +1057,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
     <col min="2" max="2" width="7.14285714285714" customWidth="1"/>
@@ -1185,6 +1191,26 @@
         <v>24</v>
       </c>
     </row>
+    <row r="7" spans="2:7">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/DataTables/Datas/#UIPanel.xlsx
+++ b/DataTables/Datas/#UIPanel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,12 @@
   </si>
   <si>
     <t>战斗界面</t>
+  </si>
+  <si>
+    <t>LoadingPanel</t>
+  </si>
+  <si>
+    <t>加载界面</t>
   </si>
 </sst>
 </file>
@@ -1057,8 +1063,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
     <col min="2" max="2" width="7.14285714285714" customWidth="1"/>
@@ -1211,6 +1217,26 @@
         <v>26</v>
       </c>
     </row>
+    <row r="8" spans="2:7">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/DataTables/Datas/#UIPanel.xlsx
+++ b/DataTables/Datas/#UIPanel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -25,9 +25,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>group</t>
-  </si>
-  <si>
     <t>allowMult</t>
   </si>
   <si>
@@ -43,9 +40,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>DUIGroup</t>
-  </si>
-  <si>
     <t>bool</t>
   </si>
   <si>
@@ -64,9 +58,6 @@
     <t>界面名称</t>
   </si>
   <si>
-    <t>界面所属组</t>
-  </si>
-  <si>
     <t>是否允许多个界面实例</t>
   </si>
   <si>
@@ -83,9 +74,6 @@
   </si>
   <si>
     <t>SettingPanel</t>
-  </si>
-  <si>
-    <t>Bottom2</t>
   </si>
   <si>
     <t>设置界面</t>
@@ -1063,18 +1051,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
     <col min="2" max="2" width="7.14285714285714" customWidth="1"/>
     <col min="3" max="3" width="11.3571428571429" customWidth="1"/>
-    <col min="4" max="4" width="11.7142857142857" customWidth="1"/>
-    <col min="5" max="6" width="22.9285714285714" customWidth="1"/>
-    <col min="7" max="7" width="9.57142857142857" customWidth="1"/>
+    <col min="4" max="5" width="22.9285714285714" customWidth="1"/>
+    <col min="6" max="6" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,151 +1077,127 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:6">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:6">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>24</v>
+      <c r="F6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:6">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
+      <c r="F7" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:6">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
+      <c r="F8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/#UIPanel.xlsx
+++ b/DataTables/Datas/#UIPanel.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -25,6 +25,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>group</t>
+  </si>
+  <si>
     <t>allowMult</t>
   </si>
   <si>
@@ -40,6 +43,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>DUIGroup</t>
+  </si>
+  <si>
     <t>bool</t>
   </si>
   <si>
@@ -58,6 +64,9 @@
     <t>界面名称</t>
   </si>
   <si>
+    <t>界面所属组</t>
+  </si>
+  <si>
     <t>是否允许多个界面实例</t>
   </si>
   <si>
@@ -74,6 +83,9 @@
   </si>
   <si>
     <t>SettingPanel</t>
+  </si>
+  <si>
+    <t>Bottom2</t>
   </si>
   <si>
     <t>设置界面</t>
@@ -1051,17 +1063,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="8.21428571428571" customWidth="1"/>
     <col min="2" max="2" width="7.14285714285714" customWidth="1"/>
     <col min="3" max="3" width="11.3571428571429" customWidth="1"/>
-    <col min="4" max="5" width="22.9285714285714" customWidth="1"/>
-    <col min="6" max="6" width="9.57142857142857" customWidth="1"/>
+    <col min="4" max="4" width="11.7142857142857" customWidth="1"/>
+    <col min="5" max="6" width="22.9285714285714" customWidth="1"/>
+    <col min="7" max="7" width="9.57142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,127 +1090,151 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:7">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="s">
-        <v>18</v>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:7">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
+      <c r="G6" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:7">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="s">
-        <v>22</v>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:7">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>24</v>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
